--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939893</v>
+        <v>125939832</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493025</v>
+        <v>493022</v>
       </c>
       <c r="R8" t="n">
-        <v>6818855</v>
+        <v>6818909</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,60 +1342,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939684</v>
+        <v>125939893</v>
       </c>
       <c r="B9" t="n">
-        <v>97215</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493073</v>
+        <v>493025</v>
       </c>
       <c r="R9" t="n">
-        <v>6818902</v>
+        <v>6818855</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,44 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939832</v>
+        <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>97215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493022</v>
+        <v>493073</v>
       </c>
       <c r="R10" t="n">
-        <v>6818909</v>
+        <v>6818902</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939894</v>
       </c>
       <c r="B2" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939599</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125939711</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125939643</v>
       </c>
       <c r="B5" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125940552</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125940572</v>
       </c>
       <c r="B7" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939832</v>
+        <v>125939893</v>
       </c>
       <c r="B8" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493022</v>
+        <v>493025</v>
       </c>
       <c r="R8" t="n">
-        <v>6818909</v>
+        <v>6818855</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939893</v>
+        <v>125939832</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493025</v>
+        <v>493022</v>
       </c>
       <c r="R9" t="n">
-        <v>6818855</v>
+        <v>6818909</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>97215</v>
+        <v>97216</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125940034</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125939631</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125939814</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939894</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939599</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125939711</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125939643</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125940552</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125940572</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125939893</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125939832</v>
       </c>
       <c r="B9" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125940034</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125939631</v>
       </c>
       <c r="B12" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125939814</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939832</v>
+        <v>125939684</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>97223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493022</v>
+        <v>493073</v>
       </c>
       <c r="R9" t="n">
-        <v>6818909</v>
+        <v>6818902</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939684</v>
+        <v>125939832</v>
       </c>
       <c r="B10" t="n">
-        <v>97222</v>
+        <v>79590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493073</v>
+        <v>493022</v>
       </c>
       <c r="R10" t="n">
-        <v>6818902</v>
+        <v>6818909</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939894</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939599</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125939711</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125939643</v>
       </c>
       <c r="B5" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125940552</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125940572</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125939893</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939684</v>
+        <v>125939832</v>
       </c>
       <c r="B9" t="n">
-        <v>97223</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493073</v>
+        <v>493022</v>
       </c>
       <c r="R9" t="n">
-        <v>6818902</v>
+        <v>6818909</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939832</v>
+        <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>97225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493022</v>
+        <v>493073</v>
       </c>
       <c r="R10" t="n">
-        <v>6818909</v>
+        <v>6818902</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125940034</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125939631</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125939814</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939893</v>
+        <v>125939832</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493025</v>
+        <v>493022</v>
       </c>
       <c r="R8" t="n">
-        <v>6818855</v>
+        <v>6818909</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939832</v>
+        <v>125939893</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493022</v>
+        <v>493025</v>
       </c>
       <c r="R9" t="n">
-        <v>6818909</v>
+        <v>6818855</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939832</v>
+        <v>125939684</v>
       </c>
       <c r="B8" t="n">
-        <v>79591</v>
+        <v>97229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493022</v>
+        <v>493073</v>
       </c>
       <c r="R8" t="n">
-        <v>6818909</v>
+        <v>6818902</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939893</v>
+        <v>125939832</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493025</v>
+        <v>493022</v>
       </c>
       <c r="R9" t="n">
-        <v>6818855</v>
+        <v>6818909</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,60 +1439,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939684</v>
+        <v>125939893</v>
       </c>
       <c r="B10" t="n">
-        <v>97229</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493073</v>
+        <v>493025</v>
       </c>
       <c r="R10" t="n">
-        <v>6818902</v>
+        <v>6818855</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939894</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939599</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125939711</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125939643</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125940552</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125940572</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939684</v>
+        <v>125939893</v>
       </c>
       <c r="B8" t="n">
-        <v>97229</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493073</v>
+        <v>493025</v>
       </c>
       <c r="R8" t="n">
-        <v>6818902</v>
+        <v>6818855</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>125939832</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,48 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939893</v>
+        <v>125939684</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>97233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493025</v>
+        <v>493073</v>
       </c>
       <c r="R10" t="n">
-        <v>6818855</v>
+        <v>6818902</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>125940034</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125939631</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125939814</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1257,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939893</v>
+        <v>125939684</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>97236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493025</v>
+        <v>493073</v>
       </c>
       <c r="R8" t="n">
-        <v>6818855</v>
+        <v>6818902</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939832</v>
+        <v>125939893</v>
       </c>
       <c r="B9" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493022</v>
+        <v>493025</v>
       </c>
       <c r="R9" t="n">
-        <v>6818909</v>
+        <v>6818855</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,44 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939684</v>
+        <v>125939832</v>
       </c>
       <c r="B10" t="n">
-        <v>97233</v>
+        <v>79595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493073</v>
+        <v>493022</v>
       </c>
       <c r="R10" t="n">
-        <v>6818902</v>
+        <v>6818909</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939894</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939599</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125939711</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125939643</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125940552</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125940572</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125939684</v>
       </c>
       <c r="B8" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939893</v>
+        <v>125939832</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493025</v>
+        <v>493022</v>
       </c>
       <c r="R9" t="n">
-        <v>6818855</v>
+        <v>6818909</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939832</v>
+        <v>125939893</v>
       </c>
       <c r="B10" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493022</v>
+        <v>493025</v>
       </c>
       <c r="R10" t="n">
-        <v>6818909</v>
+        <v>6818855</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>125940034</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125939631</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125939814</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28531-2025 artfynd.xlsx
+++ b/artfynd/A 28531-2025 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939832</v>
+        <v>125939893</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kuntmyran, Kuntmyran, Dlr</t>
+          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493022</v>
+        <v>493025</v>
       </c>
       <c r="R9" t="n">
-        <v>6818909</v>
+        <v>6818855</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939893</v>
+        <v>125939832</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Råbergsbäcken, Västra Råbergsbäcken, Dlr</t>
+          <t>Kuntmyran, Kuntmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493025</v>
+        <v>493022</v>
       </c>
       <c r="R10" t="n">
-        <v>6818855</v>
+        <v>6818909</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
